--- a/光伏配储项目/电价数据/2026/塔岭站.xlsx
+++ b/光伏配储项目/电价数据/2026/塔岭站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48222</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75558</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5401</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.55531</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47432</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.40964</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47135</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12949</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03419</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02917</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.03155</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.06734</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.02726</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15184</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.13752</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.07784999999999999</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51015</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53734</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7340599999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12281</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.19611</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6613600000000001</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.86548</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19631</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.41449</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.27701</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.98672</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28203</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.47947</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68308</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.73329</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08397</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95466</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80059</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76146</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5146499999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41773</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42763</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7174299999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88988</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94308</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50286</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5252899999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50968</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49179</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47326</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.38041</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40849</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.16222</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.02256</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.08284</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49297</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48983</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50407</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12383</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.01137</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.51225</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.04061</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.02228</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>-0.02267</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.02625</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.78361</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.25699</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.14013</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.23272</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5439299999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59293</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74346</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.75448</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16155</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24995</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.13082</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8377100000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20535</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10625</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25644</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02218</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09048</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65149</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98338</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95766</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77967</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8861599999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7358300000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.78085</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.72649</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.75959</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42987</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44527</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33494</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5133099999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49335</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44479</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47794</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44176</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21566</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.18722</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.78042</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.46267</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.21972</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.41331</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.50659</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.47137</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.4317</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28544</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62115</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64611</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46619</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5467000000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48373</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61124</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61775</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.56953</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55729</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7162999999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.60117</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.51778</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55157</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34235</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51483</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3664</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38952</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43136</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.08115</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.04809</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.12391</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.0395</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5611799999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17378</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15814</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12119</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39736</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6243</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44373</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40691</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47498</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50976</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46713</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48554</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.5487300000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43954</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55814</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49498</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46941</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5047699999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32138</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29136</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.07517</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26681</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.15627</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.09426999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.08616</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.00876</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.15901</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.15835</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.03879999999999999</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.00365</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01871</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.42207</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39533</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42532</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4874</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42514</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.5488200000000001</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37268</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.8683500000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5782200000000001</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5365800000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.55057</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.43701</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.62324</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.43333</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10214</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00508</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.1968</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04458</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26154</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04373</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04912</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34807</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32382</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45789</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854800000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86921</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57743</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.54291</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43221</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.45912</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6721900000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50682</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62964</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.81953</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8844099999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.50084</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6714600000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.5013500000000001</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.05627</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8115</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87517</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.5192599999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.91435</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8454199999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59049</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47946</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.5448500000000001</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48732</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44713</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37274</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9369700000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47848</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45933</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55638</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.47028</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44626</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2193</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.08782999999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20087</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28594</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25874</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.39102</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.53847</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4753500000000001</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.47961</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7925800000000001</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43669</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9504600000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48435</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20453</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.73149</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82347</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68262</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.81438</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.60415</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.52855</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46611</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.50071</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43683</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.48126</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.6199600000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43644</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45878</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48799</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.51822</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.5545800000000001</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41942</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44598</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.52627</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43259</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.47185</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.5158200000000001</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47815</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51844</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.46488</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.63447</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.57156</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15737</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01727</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30146</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26452</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25916</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.65677</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.55287</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.03027</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.55955</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52606</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.42019</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51393</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.43312</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.37221</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.52354</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40717</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.41364</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.43562</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.55311</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5219400000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5638300000000001</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5358999999999999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.50203</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21423</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.06998</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.09778000000000001</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11511</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.08231000000000001</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.08995</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26519</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10122</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.22985</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08543000000000001</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25634</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.12617</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05128</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.02752</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06314</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05494</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07362</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42864</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45825</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40405</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.44261</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5492999999999999</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46728</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.5482899999999999</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5344500000000001</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.53028</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.5369299999999999</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46313</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.41127</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.39247</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.68626</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.57163</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49842</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48662</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.43322</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39886</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43421</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.54755</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.43247</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39952</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36592</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26675</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2347</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17296</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.19322</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>-0.04261</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.03603</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>-0.02535</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40716</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40607</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5267200000000001</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.42141</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47596</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42703</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39613</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40367</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6386499999999999</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.6460199999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38434</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43883</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.40253</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4549</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.13571</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43569</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67957</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51774</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.46973</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43691</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25938</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26366</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17678</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.18326</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27766</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.25489</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.55535</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.43553</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.12759</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43518</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43646</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.5821900000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48192</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46742</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72078</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.06639</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.9069199999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.73187</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52922</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42834</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5205</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43868</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.37641</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42649</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.47044</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.45024</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3781</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.48038</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42792</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44876</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44645</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.4721</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36921</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.6053200000000001</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.39066</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42303</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43573</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39534</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.67552</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.0898</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.52619</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45595</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37532</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40299</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.39134</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42869</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.10751</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.19933</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.1247</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.25186</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25156</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15318</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21643</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.25803</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5698099999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.5112300000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47099</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6815</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63906</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65759</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.65283</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8492999999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.62563</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.20896</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.6775399999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.4652</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6099199999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.50639</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48766</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.39075</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.59492</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.73278</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.6364299999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.91359</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.48246</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.47216</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.46112</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43827</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.49084</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48785</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.48024</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46934</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.56248</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.73677</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.62818</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.54326</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.61709</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53927</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46525</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.54835</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.47308</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.64747</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.60997</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.18568</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29384</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37301</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.42084</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.6019500000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.54022</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.64159</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.64398</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.7107899999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.95839</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.18825</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.30585</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9418200000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.11299</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.9269299999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.70245</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.15655</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6425599999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6919</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.56555</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.59509</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.59192</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5799299999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.5716100000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.7004900000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49854</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.52171</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.53166</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43565</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45608</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.58012</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4708</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.45309</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43764</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41816</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40902</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40629</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26328</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5178400000000001</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.02188</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.10306</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.02997</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38372</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4932</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.47309</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45513</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5255599999999999</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42759</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.49646</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.50761</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.52336</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40362</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46852</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47816</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.43577</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.47412</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.51423</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.48828</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.53211</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.51258</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.46946</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.62898</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.48145</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49579</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.48519</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.4719</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.6318400000000001</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.60081</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.59482</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.47151</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.60888</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.44297</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.47093</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.5696</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43579</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.45226</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45878</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.4653</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.55422</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.47182</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.5524</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.56911</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.49795</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.56908</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.17959</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21019</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.22882</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.07165000000000001</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.26997</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.08709</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.10628</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18115</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22207</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27382</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21356</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38882</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.46237</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47757</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.47488</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44215</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43683</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.49323</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50839</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.46729</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.4679700000000001</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.428</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.51515</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.48713</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.5264099999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.51736</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.51736</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.51483</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.51873</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.51106</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.5116700000000001</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.5267200000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.52627</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.5297500000000001</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03414</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0009699999999999999</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15164</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02284</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01488</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02948</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03722</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00152</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03619</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03557</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20575</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26905</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.5224299999999999</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42319</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.54275</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39077</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.41168</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.1974</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.02684</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49598</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8865700000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5291699999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.54373</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5989099999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.45341</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.51339</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.48781</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.48218</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.64507</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46873</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44241</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.66775</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.57784</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.65942</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.60326</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.66089</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.62874</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.61054</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.6357</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.67796</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46627</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.5428099999999999</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.60133</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52528</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.52467</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.42129</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9117999999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87346</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.03465</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.04811</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04817</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04894</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04276</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04852</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42928</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41281</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39883</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.05196</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.16455</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.12192</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.00109</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.15018</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.0531</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.15715</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8636</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.86186</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.86599</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9628</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.1528</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.15313</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.14686</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.42372</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.60842</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.90046</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.48942</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51959</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.6279600000000001</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.5230900000000001</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.48971</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.42766</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.4319</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.67131</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.47633</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.62887</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.5417000000000001</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.51163</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.50915</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62003</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.67757</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.52738</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.21913</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.16007</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26968</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26082</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.42104</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.63385</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.25719</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5099399999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9219700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.6169</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.55084</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.54157</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6808</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42814</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.41445</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.40494</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.4997799999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.51697</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.48667</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.48081</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40845</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.55184</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.8651599999999999</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.0188</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8455199999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.78451</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.60364</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.01573</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8325399999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46882</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.58405</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5578</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65977</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8168099999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.92941</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.81428</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.61539</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.61821</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43902</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.54472</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5426</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.45086</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.45031</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40405</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.53176</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.45311</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.44003</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.46301</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40101</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44598</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45552</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66639</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7097100000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.78831</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54804</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.7819199999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48454</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6176799999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.95147</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5449700000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5285700000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54316</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.02157</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.48364</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.40021</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40833</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.6216799999999999</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17748</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17451</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18498</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01445</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26499</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00878</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.03032</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04286</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11114</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02733</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23285</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.1834</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20843</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40393</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.54732</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44086</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.52132</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43861</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42742</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44764</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.42049</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.26766</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.22806</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.46644</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43607</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40696</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41709</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40556</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39623</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41219</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26697</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28455</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.09967000000000001</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1315</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43324</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40687</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41086</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41629</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38979</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48445</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45658</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.40172</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14653</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19979</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02257</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24226</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03392</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04704</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03604</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04989</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.0488</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.02153</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22262</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14794</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26427</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2591</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42332</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40766</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.5112099999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3975</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40904</v>
       </c>
     </row>
   </sheetData>
